--- a/高一107花名册新.xlsx
+++ b/高一107花名册新.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="686">
   <si>
     <t>高一107花名册</t>
   </si>
@@ -1889,6 +1889,27 @@
   </si>
   <si>
     <t>13938335368</t>
+  </si>
+  <si>
+    <t>姚丁恺</t>
+  </si>
+  <si>
+    <t>410902200908067577</t>
+  </si>
+  <si>
+    <t>濮阳市华龙区卫河中路星海化工厂家属院5号楼1单元102</t>
+  </si>
+  <si>
+    <t>周艳芬</t>
+  </si>
+  <si>
+    <t>13461609921</t>
+  </si>
+  <si>
+    <t>姚永现</t>
+  </si>
+  <si>
+    <t>13503930002</t>
   </si>
   <si>
     <t>优秀学生干部</t>
@@ -3566,7 +3587,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -6302,6 +6323,41 @@
       </c>
       <c r="K78" s="3" t="s">
         <v>616</v>
+      </c>
+    </row>
+    <row r="79" ht="40.5" spans="1:11">
+      <c r="A79" s="3">
+        <v>77</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>618</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -6340,7 +6396,7 @@
         <v>443</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2" ht="18.75" spans="1:4">
@@ -6354,7 +6410,7 @@
         <v>98</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
     </row>
     <row r="3" ht="18.75" spans="1:4">
@@ -6368,7 +6424,7 @@
         <v>515</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="4" ht="18.75" spans="1:4">
@@ -6382,7 +6438,7 @@
         <v>366</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="5" ht="18.75" spans="1:4">
@@ -6390,13 +6446,13 @@
         <v>107</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>52</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="6" ht="18.75" spans="1:4">
@@ -6410,7 +6466,7 @@
         <v>418</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="7" ht="18.75" spans="1:4">
@@ -6424,7 +6480,7 @@
         <v>76</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="8" ht="18.75" spans="1:4">
@@ -6438,7 +6494,7 @@
         <v>475</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" ht="18.75" spans="1:4">
@@ -6452,12 +6508,12 @@
         <v>537</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6471,7 +6527,7 @@
         <v>233</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6479,13 +6535,13 @@
         <v>107</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6499,7 +6555,7 @@
         <v>130</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6513,7 +6569,7 @@
         <v>587</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6527,7 +6583,7 @@
         <v>354</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -6541,12 +6597,12 @@
         <v>595</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -6627,11 +6683,11 @@
   <sheetData>
     <row r="1" ht="17.4" customHeight="1" spans="5:16">
       <c r="E1" s="7" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="8" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
@@ -6645,11 +6701,11 @@
     </row>
     <row r="2" ht="17.4" customHeight="1" spans="5:16">
       <c r="E2" s="7" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="9" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="9"/>
@@ -6663,7 +6719,7 @@
     </row>
     <row r="3" ht="17.4" customHeight="1" spans="5:16">
       <c r="E3" s="7" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="9"/>
@@ -6679,7 +6735,7 @@
     </row>
     <row r="4" ht="17.4" customHeight="1" spans="5:16">
       <c r="E4" s="7" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="9"/>
@@ -6695,11 +6751,11 @@
     </row>
     <row r="5" ht="17.4" customHeight="1" spans="5:16">
       <c r="E5" s="7" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="10" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
@@ -6713,11 +6769,11 @@
     </row>
     <row r="6" ht="17.4" customHeight="1" spans="5:16">
       <c r="E6" s="7" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="11" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="H6" s="11"/>
       <c r="I6" s="11"/>
@@ -6731,54 +6787,54 @@
     </row>
     <row r="7" ht="14.25" spans="5:16">
       <c r="E7" s="12" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="O7" s="13" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="P7" s="13" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="5:16">
       <c r="E8" s="14" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>490</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
@@ -6791,16 +6847,16 @@
     </row>
     <row r="9" ht="14.25" spans="5:16">
       <c r="E9" s="14" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I9" s="15"/>
       <c r="J9" s="15"/>
@@ -6813,16 +6869,16 @@
     </row>
     <row r="10" ht="14.25" spans="5:16">
       <c r="E10" s="14" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>137</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="15"/>
@@ -6835,16 +6891,16 @@
     </row>
     <row r="11" ht="14.25" spans="5:16">
       <c r="E11" s="14" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>200</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="15"/>
@@ -6857,13 +6913,13 @@
     </row>
     <row r="12" ht="14.25" spans="5:16">
       <c r="E12" s="14" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>274</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="15"/>
@@ -6877,13 +6933,13 @@
     </row>
     <row r="13" ht="14.25" spans="5:16">
       <c r="E13" s="14" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>184</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="15"/>
@@ -6897,13 +6953,13 @@
     </row>
     <row r="14" ht="14.25" spans="5:16">
       <c r="E14" s="14" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>365</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="15"/>
@@ -6917,13 +6973,13 @@
     </row>
     <row r="15" ht="14.25" spans="5:16">
       <c r="E15" s="14" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>83</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="15"/>
@@ -6937,13 +6993,13 @@
     </row>
     <row r="16" ht="14.25" spans="5:16">
       <c r="E16" s="14" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>58</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="15"/>
@@ -6957,54 +7013,54 @@
     </row>
     <row r="17" ht="14.25" spans="5:16">
       <c r="E17" s="12" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="O17" s="13" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="P17" s="13" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="5:16">
       <c r="E18" s="14" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>554</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
@@ -7017,16 +7073,16 @@
     </row>
     <row r="19" ht="14.25" spans="5:16">
       <c r="E19" s="14" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>529</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="15"/>
@@ -7039,16 +7095,16 @@
     </row>
     <row r="20" ht="14.25" spans="5:16">
       <c r="E20" s="14" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>151</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
@@ -7061,16 +7117,16 @@
     </row>
     <row r="21" ht="14.25" spans="5:16">
       <c r="E21" s="14" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>408</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
@@ -7083,16 +7139,16 @@
     </row>
     <row r="22" ht="14.25" spans="5:16">
       <c r="E22" s="14" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>192</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
@@ -7105,13 +7161,13 @@
     </row>
     <row r="23" ht="14.25" spans="5:16">
       <c r="E23" s="14" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>563</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="H23" s="18"/>
       <c r="I23" s="15"/>
@@ -7125,13 +7181,13 @@
     </row>
     <row r="24" ht="14.25" spans="5:16">
       <c r="E24" s="14" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="F24" s="18" t="s">
         <v>75</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="H24" s="15"/>
       <c r="I24" s="15"/>
@@ -7145,16 +7201,16 @@
     </row>
     <row r="25" ht="14.25" spans="5:16">
       <c r="E25" s="14" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="F25" s="18" t="s">
         <v>175</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="H25" s="15" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="I25" s="15"/>
       <c r="J25" s="15"/>
@@ -7167,13 +7223,13 @@
     </row>
     <row r="26" ht="14.25" spans="5:16">
       <c r="E26" s="14" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="F26" s="18" t="s">
         <v>218</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="H26" s="15"/>
       <c r="I26" s="15"/>
@@ -7242,7 +7298,7 @@
         <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>14</v>
@@ -7254,7 +7310,7 @@
         <v>327</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>328</v>
@@ -7268,7 +7324,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>23</v>
@@ -7280,7 +7336,7 @@
         <v>335</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>336</v>
@@ -7294,7 +7350,7 @@
         <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>37</v>
@@ -7306,7 +7362,7 @@
         <v>344</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>345</v>
@@ -7320,7 +7376,7 @@
         <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>45</v>
@@ -7332,7 +7388,7 @@
         <v>353</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>354</v>
@@ -7346,7 +7402,7 @@
         <v>51</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>52</v>
@@ -7358,7 +7414,7 @@
         <v>365</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>366</v>
@@ -7372,7 +7428,7 @@
         <v>58</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>59</v>
@@ -7384,7 +7440,7 @@
         <v>374</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>375</v>
@@ -7398,7 +7454,7 @@
         <v>67</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>68</v>
@@ -7410,7 +7466,7 @@
         <v>383</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>384</v>
@@ -7424,7 +7480,7 @@
         <v>75</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>76</v>
@@ -7436,7 +7492,7 @@
         <v>390</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>391</v>
@@ -7450,7 +7506,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>84</v>
@@ -7462,7 +7518,7 @@
         <v>399</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>400</v>
@@ -7476,7 +7532,7 @@
         <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>98</v>
@@ -7488,7 +7544,7 @@
         <v>408</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>409</v>
@@ -7502,7 +7558,7 @@
         <v>113</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>114</v>
@@ -7514,7 +7570,7 @@
         <v>417</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>418</v>
@@ -7528,7 +7584,7 @@
         <v>121</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>122</v>
@@ -7540,7 +7596,7 @@
         <v>426</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>427</v>
@@ -7554,7 +7610,7 @@
         <v>129</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>130</v>
@@ -7566,7 +7622,7 @@
         <v>435</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>436</v>
@@ -7580,7 +7636,7 @@
         <v>137</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>138</v>
@@ -7592,7 +7648,7 @@
         <v>442</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>443</v>
@@ -7606,7 +7662,7 @@
         <v>143</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>144</v>
@@ -7618,7 +7674,7 @@
         <v>451</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>452</v>
@@ -7632,7 +7688,7 @@
         <v>151</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>152</v>
@@ -7644,7 +7700,7 @@
         <v>458</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>459</v>
@@ -7658,7 +7714,7 @@
         <v>159</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>160</v>
@@ -7670,7 +7726,7 @@
         <v>466</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>467</v>
@@ -7684,7 +7740,7 @@
         <v>168</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>169</v>
@@ -7696,7 +7752,7 @@
         <v>474</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>475</v>
@@ -7710,7 +7766,7 @@
         <v>175</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>176</v>
@@ -7722,7 +7778,7 @@
         <v>481</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>482</v>
@@ -7736,7 +7792,7 @@
         <v>184</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>185</v>
@@ -7748,7 +7804,7 @@
         <v>490</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>491</v>
@@ -7759,13 +7815,13 @@
         <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="E22" s="1">
         <v>107</v>
@@ -7774,7 +7830,7 @@
         <v>498</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>499</v>
@@ -7788,7 +7844,7 @@
         <v>192</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>193</v>
@@ -7800,7 +7856,7 @@
         <v>507</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>508</v>
@@ -7814,7 +7870,7 @@
         <v>200</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>201</v>
@@ -7826,7 +7882,7 @@
         <v>514</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>515</v>
@@ -7840,7 +7896,7 @@
         <v>209</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>210</v>
@@ -7852,7 +7908,7 @@
         <v>521</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>522</v>
@@ -7866,7 +7922,7 @@
         <v>218</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>219</v>
@@ -7878,7 +7934,7 @@
         <v>529</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>530</v>
@@ -7892,7 +7948,7 @@
         <v>225</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>226</v>
@@ -7904,7 +7960,7 @@
         <v>536</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>537</v>
@@ -7918,7 +7974,7 @@
         <v>232</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>233</v>
@@ -7930,7 +7986,7 @@
         <v>545</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>546</v>
@@ -7944,7 +8000,7 @@
         <v>241</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>242</v>
@@ -7956,7 +8012,7 @@
         <v>554</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>555</v>
@@ -7970,7 +8026,7 @@
         <v>250</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>251</v>
@@ -7982,7 +8038,7 @@
         <v>571</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>572</v>
@@ -7996,7 +8052,7 @@
         <v>257</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>258</v>
@@ -8008,7 +8064,7 @@
         <v>580</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>581</v>
@@ -8022,7 +8078,7 @@
         <v>265</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>266</v>
@@ -8034,7 +8090,7 @@
         <v>586</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>587</v>
@@ -8048,7 +8104,7 @@
         <v>295</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>296</v>
@@ -8060,7 +8116,7 @@
         <v>594</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>595</v>
@@ -8074,7 +8130,7 @@
         <v>274</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D34" s="35" t="s">
         <v>275</v>
@@ -8086,7 +8142,7 @@
         <v>601</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>602</v>
@@ -8100,7 +8156,7 @@
         <v>281</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>282</v>
@@ -8112,7 +8168,7 @@
         <v>608</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>609</v>
@@ -8126,7 +8182,7 @@
         <v>303</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>304</v>
@@ -8138,7 +8194,7 @@
         <v>104</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>105</v>
@@ -8152,7 +8208,7 @@
         <v>311</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>312</v>
@@ -8164,7 +8220,7 @@
         <v>563</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>564</v>
@@ -8178,7 +8234,7 @@
         <v>320</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>321</v>
@@ -8190,7 +8246,7 @@
         <v>290</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H38" s="36" t="s">
         <v>291</v>
@@ -8204,7 +8260,7 @@
         <v>360</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>361</v>
